--- a/artfynd/A 30224-2025 artfynd.xlsx
+++ b/artfynd/A 30224-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126686418</v>
       </c>
       <c r="B2" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126686336</v>
       </c>
       <c r="B3" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126686514</v>
       </c>
       <c r="B4" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>126686314</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,48 +1083,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126675620</v>
+        <v>126686841</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsåsen, Långsåsen, Dlr</t>
+          <t>Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477793</v>
+        <v>477792</v>
       </c>
       <c r="R6" t="n">
-        <v>6731721</v>
+        <v>6731817</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1151,49 +1154,40 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126686841</v>
+        <v>126686530</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477792</v>
+        <v>477553</v>
       </c>
       <c r="R7" t="n">
-        <v>6731817</v>
+        <v>6731763</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1258,12 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,51 +1285,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126686530</v>
+        <v>126675620</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsåsen, Dlr</t>
+          <t>Långsåsen, Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477553</v>
+        <v>477793</v>
       </c>
       <c r="R8" t="n">
-        <v>6731763</v>
+        <v>6731721</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,12 +1350,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,19 +1374,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         <v>126686823</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>126686797</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>126686471</v>
       </c>
       <c r="B11" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126686832</v>
+        <v>126686767</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477784</v>
+        <v>477671</v>
       </c>
       <c r="R12" t="n">
-        <v>6731836</v>
+        <v>6731817</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126686767</v>
+        <v>126686832</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477671</v>
+        <v>477784</v>
       </c>
       <c r="R13" t="n">
-        <v>6731817</v>
+        <v>6731836</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126686450</v>
+        <v>126686794</v>
       </c>
       <c r="B14" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477654</v>
+        <v>477711</v>
       </c>
       <c r="R14" t="n">
-        <v>6731777</v>
+        <v>6731832</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126686794</v>
+        <v>126686450</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477711</v>
+        <v>477654</v>
       </c>
       <c r="R15" t="n">
-        <v>6731832</v>
+        <v>6731777</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126686813</v>
+        <v>126686803</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477736</v>
+        <v>477751</v>
       </c>
       <c r="R16" t="n">
-        <v>6731859</v>
+        <v>6731845</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126686803</v>
+        <v>126686813</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477751</v>
+        <v>477736</v>
       </c>
       <c r="R17" t="n">
-        <v>6731845</v>
+        <v>6731859</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2304,7 +2304,7 @@
         <v>126686777</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126686786</v>
+        <v>126686680</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477713</v>
+        <v>477539</v>
       </c>
       <c r="R19" t="n">
-        <v>6731860</v>
+        <v>6731648</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126686680</v>
+        <v>126686407</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>91339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,24 +2514,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2541,10 +2545,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477539</v>
+        <v>477671</v>
       </c>
       <c r="R20" t="n">
-        <v>6731648</v>
+        <v>6731781</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2571,12 +2575,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2604,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126686407</v>
+        <v>126686786</v>
       </c>
       <c r="B21" t="n">
-        <v>91265</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,28 +2619,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477671</v>
+        <v>477713</v>
       </c>
       <c r="R21" t="n">
-        <v>6731781</v>
+        <v>6731860</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2712,7 +2712,7 @@
         <v>126686291</v>
       </c>
       <c r="B22" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>126686752</v>
       </c>
       <c r="B23" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>126675585</v>
       </c>
       <c r="B24" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>126686757</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 30224-2025 artfynd.xlsx
+++ b/artfynd/A 30224-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126686418</v>
+        <v>126686336</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>91325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477668</v>
+        <v>477695</v>
       </c>
       <c r="R2" t="n">
-        <v>6731773</v>
+        <v>6731734</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126686336</v>
+        <v>126686418</v>
       </c>
       <c r="B3" t="n">
-        <v>91319</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477695</v>
+        <v>477668</v>
       </c>
       <c r="R3" t="n">
-        <v>6731734</v>
+        <v>6731773</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -880,7 +880,7 @@
         <v>126686514</v>
       </c>
       <c r="B4" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>126686314</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,51 +1083,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126686841</v>
+        <v>126675620</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsåsen, Dlr</t>
+          <t>Långsåsen, Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477792</v>
+        <v>477793</v>
       </c>
       <c r="R6" t="n">
-        <v>6731817</v>
+        <v>6731721</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1154,40 +1151,49 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126686530</v>
+        <v>126686841</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477553</v>
+        <v>477792</v>
       </c>
       <c r="R7" t="n">
-        <v>6731763</v>
+        <v>6731817</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1252,12 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,48 +1291,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126675620</v>
+        <v>126686530</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsåsen, Långsåsen, Dlr</t>
+          <t>Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477793</v>
+        <v>477553</v>
       </c>
       <c r="R8" t="n">
-        <v>6731721</v>
+        <v>6731763</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,22 +1359,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,18 +1373,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1395,7 +1395,7 @@
         <v>126686823</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>126686797</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>126686471</v>
       </c>
       <c r="B11" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>126686767</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>126686832</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126686794</v>
+        <v>126686450</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477711</v>
+        <v>477654</v>
       </c>
       <c r="R14" t="n">
-        <v>6731832</v>
+        <v>6731777</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126686450</v>
+        <v>126686794</v>
       </c>
       <c r="B15" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477654</v>
+        <v>477711</v>
       </c>
       <c r="R15" t="n">
-        <v>6731777</v>
+        <v>6731832</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,7 +2102,7 @@
         <v>126686803</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>126686813</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>126686777</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126686680</v>
+        <v>126686291</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>91345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2413,24 +2413,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2440,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477539</v>
+        <v>477757</v>
       </c>
       <c r="R19" t="n">
-        <v>6731648</v>
+        <v>6731689</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2470,12 +2474,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2503,10 +2507,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126686407</v>
+        <v>126686680</v>
       </c>
       <c r="B20" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2514,28 +2518,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477671</v>
+        <v>477539</v>
       </c>
       <c r="R20" t="n">
-        <v>6731781</v>
+        <v>6731648</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126686786</v>
+        <v>126686407</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>91345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,24 +2619,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2646,10 +2650,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477713</v>
+        <v>477671</v>
       </c>
       <c r="R21" t="n">
-        <v>6731860</v>
+        <v>6731781</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2676,12 +2680,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2709,10 +2713,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126686291</v>
+        <v>126686786</v>
       </c>
       <c r="B22" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,28 +2724,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477757</v>
+        <v>477713</v>
       </c>
       <c r="R22" t="n">
-        <v>6731689</v>
+        <v>6731860</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2817,7 @@
         <v>126686752</v>
       </c>
       <c r="B23" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>126675585</v>
       </c>
       <c r="B24" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>126686757</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 30224-2025 artfynd.xlsx
+++ b/artfynd/A 30224-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126686336</v>
+        <v>126686418</v>
       </c>
       <c r="B2" t="n">
-        <v>91325</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477695</v>
+        <v>477668</v>
       </c>
       <c r="R2" t="n">
-        <v>6731734</v>
+        <v>6731773</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126686418</v>
+        <v>126686336</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>91325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477668</v>
+        <v>477695</v>
       </c>
       <c r="R3" t="n">
-        <v>6731773</v>
+        <v>6731734</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -1083,48 +1083,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126675620</v>
+        <v>126686841</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsåsen, Långsåsen, Dlr</t>
+          <t>Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477793</v>
+        <v>477792</v>
       </c>
       <c r="R6" t="n">
-        <v>6731721</v>
+        <v>6731817</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1151,46 +1154,37 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126686841</v>
+        <v>126686530</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1228,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477792</v>
+        <v>477553</v>
       </c>
       <c r="R7" t="n">
-        <v>6731817</v>
+        <v>6731763</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1258,12 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,51 +1285,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126686530</v>
+        <v>126675620</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsåsen, Dlr</t>
+          <t>Långsåsen, Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477553</v>
+        <v>477793</v>
       </c>
       <c r="R8" t="n">
-        <v>6731763</v>
+        <v>6731721</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,12 +1350,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,19 +1374,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126686450</v>
+        <v>126686794</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477654</v>
+        <v>477711</v>
       </c>
       <c r="R14" t="n">
-        <v>6731777</v>
+        <v>6731832</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126686794</v>
+        <v>126686450</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477711</v>
+        <v>477654</v>
       </c>
       <c r="R15" t="n">
-        <v>6731832</v>
+        <v>6731777</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126686291</v>
+        <v>126686680</v>
       </c>
       <c r="B19" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2413,28 +2413,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2444,10 +2440,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477757</v>
+        <v>477539</v>
       </c>
       <c r="R19" t="n">
-        <v>6731689</v>
+        <v>6731648</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2474,12 +2470,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2507,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126686680</v>
+        <v>126686407</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>91345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2518,24 +2514,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477539</v>
+        <v>477671</v>
       </c>
       <c r="R20" t="n">
-        <v>6731648</v>
+        <v>6731781</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126686407</v>
+        <v>126686786</v>
       </c>
       <c r="B21" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,28 +2619,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2650,10 +2646,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477671</v>
+        <v>477713</v>
       </c>
       <c r="R21" t="n">
-        <v>6731781</v>
+        <v>6731860</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2680,12 +2676,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2713,10 +2709,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126686786</v>
+        <v>126686291</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>91345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2724,24 +2720,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477713</v>
+        <v>477757</v>
       </c>
       <c r="R22" t="n">
-        <v>6731860</v>
+        <v>6731689</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 30224-2025 artfynd.xlsx
+++ b/artfynd/A 30224-2025 artfynd.xlsx
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126686794</v>
+        <v>126686450</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477711</v>
+        <v>477654</v>
       </c>
       <c r="R14" t="n">
-        <v>6731832</v>
+        <v>6731777</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126686450</v>
+        <v>126686794</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477654</v>
+        <v>477711</v>
       </c>
       <c r="R15" t="n">
-        <v>6731777</v>
+        <v>6731832</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30224-2025 artfynd.xlsx
+++ b/artfynd/A 30224-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126686418</v>
+        <v>126686336</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>91326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477668</v>
+        <v>477695</v>
       </c>
       <c r="R2" t="n">
-        <v>6731773</v>
+        <v>6731734</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126686336</v>
+        <v>126686418</v>
       </c>
       <c r="B3" t="n">
-        <v>91325</v>
+        <v>79632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477695</v>
+        <v>477668</v>
       </c>
       <c r="R3" t="n">
-        <v>6731734</v>
+        <v>6731773</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -880,7 +880,7 @@
         <v>126686514</v>
       </c>
       <c r="B4" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,51 +1083,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126686841</v>
+        <v>126675620</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsåsen, Dlr</t>
+          <t>Långsåsen, Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477792</v>
+        <v>477793</v>
       </c>
       <c r="R6" t="n">
-        <v>6731817</v>
+        <v>6731721</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1154,37 +1151,46 @@
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126686530</v>
+        <v>126686841</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1222,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477553</v>
+        <v>477792</v>
       </c>
       <c r="R7" t="n">
-        <v>6731763</v>
+        <v>6731817</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1252,12 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,48 +1291,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126675620</v>
+        <v>126686530</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsåsen, Långsåsen, Dlr</t>
+          <t>Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477793</v>
+        <v>477553</v>
       </c>
       <c r="R8" t="n">
-        <v>6731721</v>
+        <v>6731763</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,22 +1359,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,18 +1373,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2506,7 +2506,7 @@
         <v>126686407</v>
       </c>
       <c r="B20" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>126686291</v>
       </c>
       <c r="B22" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>126686752</v>
       </c>
       <c r="B23" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>126675585</v>
       </c>
       <c r="B24" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 30224-2025 artfynd.xlsx
+++ b/artfynd/A 30224-2025 artfynd.xlsx
@@ -1083,48 +1083,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126675620</v>
+        <v>126686841</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långsåsen, Långsåsen, Dlr</t>
+          <t>Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477793</v>
+        <v>477792</v>
       </c>
       <c r="R6" t="n">
-        <v>6731721</v>
+        <v>6731817</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1151,46 +1154,37 @@
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-15</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126686841</v>
+        <v>126686530</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1228,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477792</v>
+        <v>477553</v>
       </c>
       <c r="R7" t="n">
-        <v>6731817</v>
+        <v>6731763</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1258,12 +1252,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,51 +1285,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126686530</v>
+        <v>126675620</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsåsen, Dlr</t>
+          <t>Långsåsen, Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477553</v>
+        <v>477793</v>
       </c>
       <c r="R8" t="n">
-        <v>6731763</v>
+        <v>6731721</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,12 +1350,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,19 +1374,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126686767</v>
+        <v>126686832</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477671</v>
+        <v>477784</v>
       </c>
       <c r="R12" t="n">
-        <v>6731817</v>
+        <v>6731836</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1796,7 +1796,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126686832</v>
+        <v>126686767</v>
       </c>
       <c r="B13" t="n">
         <v>79014</v>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477784</v>
+        <v>477671</v>
       </c>
       <c r="R13" t="n">
-        <v>6731836</v>
+        <v>6731817</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126686803</v>
+        <v>126686777</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477751</v>
+        <v>477692</v>
       </c>
       <c r="R16" t="n">
-        <v>6731845</v>
+        <v>6731846</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2200,7 +2200,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126686813</v>
+        <v>126686803</v>
       </c>
       <c r="B17" t="n">
         <v>79014</v>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477736</v>
+        <v>477751</v>
       </c>
       <c r="R17" t="n">
-        <v>6731859</v>
+        <v>6731845</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2301,7 +2301,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126686777</v>
+        <v>126686813</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477692</v>
+        <v>477736</v>
       </c>
       <c r="R18" t="n">
-        <v>6731846</v>
+        <v>6731859</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126686680</v>
+        <v>126686786</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477539</v>
+        <v>477713</v>
       </c>
       <c r="R19" t="n">
-        <v>6731648</v>
+        <v>6731860</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126686407</v>
+        <v>126686291</v>
       </c>
       <c r="B20" t="n">
         <v>91346</v>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477671</v>
+        <v>477757</v>
       </c>
       <c r="R20" t="n">
-        <v>6731781</v>
+        <v>6731689</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2608,7 +2608,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126686786</v>
+        <v>126686680</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477713</v>
+        <v>477539</v>
       </c>
       <c r="R21" t="n">
-        <v>6731860</v>
+        <v>6731648</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126686291</v>
+        <v>126686407</v>
       </c>
       <c r="B22" t="n">
         <v>91346</v>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477757</v>
+        <v>477671</v>
       </c>
       <c r="R22" t="n">
-        <v>6731689</v>
+        <v>6731781</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>

--- a/artfynd/A 30224-2025 artfynd.xlsx
+++ b/artfynd/A 30224-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126686336</v>
+        <v>126686418</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477695</v>
+        <v>477668</v>
       </c>
       <c r="R2" t="n">
-        <v>6731734</v>
+        <v>6731773</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126686418</v>
+        <v>126686336</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>91319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477668</v>
+        <v>477695</v>
       </c>
       <c r="R3" t="n">
-        <v>6731773</v>
+        <v>6731734</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -880,7 +880,7 @@
         <v>126686514</v>
       </c>
       <c r="B4" t="n">
-        <v>91346</v>
+        <v>91339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>126686314</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>126686841</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>126686530</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>126686823</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         <v>126686797</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>126686471</v>
       </c>
       <c r="B11" t="n">
-        <v>79603</v>
+        <v>79600</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126686832</v>
+        <v>126686767</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477784</v>
+        <v>477671</v>
       </c>
       <c r="R12" t="n">
-        <v>6731836</v>
+        <v>6731817</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126686767</v>
+        <v>126686832</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477671</v>
+        <v>477784</v>
       </c>
       <c r="R13" t="n">
-        <v>6731817</v>
+        <v>6731836</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126686450</v>
+        <v>126686794</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477654</v>
+        <v>477711</v>
       </c>
       <c r="R14" t="n">
-        <v>6731777</v>
+        <v>6731832</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,10 +1998,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126686794</v>
+        <v>126686450</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>78769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2009,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477711</v>
+        <v>477654</v>
       </c>
       <c r="R15" t="n">
-        <v>6731832</v>
+        <v>6731777</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126686777</v>
+        <v>126686803</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477692</v>
+        <v>477751</v>
       </c>
       <c r="R16" t="n">
-        <v>6731846</v>
+        <v>6731845</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2200,10 +2200,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126686803</v>
+        <v>126686813</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477751</v>
+        <v>477736</v>
       </c>
       <c r="R17" t="n">
-        <v>6731845</v>
+        <v>6731859</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126686813</v>
+        <v>126686777</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477736</v>
+        <v>477692</v>
       </c>
       <c r="R18" t="n">
-        <v>6731859</v>
+        <v>6731846</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126686786</v>
+        <v>126686680</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477713</v>
+        <v>477539</v>
       </c>
       <c r="R19" t="n">
-        <v>6731860</v>
+        <v>6731648</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126686291</v>
+        <v>126686407</v>
       </c>
       <c r="B20" t="n">
-        <v>91346</v>
+        <v>91339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477757</v>
+        <v>477671</v>
       </c>
       <c r="R20" t="n">
-        <v>6731689</v>
+        <v>6731781</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126686680</v>
+        <v>126686786</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477539</v>
+        <v>477713</v>
       </c>
       <c r="R21" t="n">
-        <v>6731648</v>
+        <v>6731860</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126686407</v>
+        <v>126686291</v>
       </c>
       <c r="B22" t="n">
-        <v>91346</v>
+        <v>91339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477671</v>
+        <v>477757</v>
       </c>
       <c r="R22" t="n">
-        <v>6731781</v>
+        <v>6731689</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2817,7 +2817,7 @@
         <v>126686752</v>
       </c>
       <c r="B23" t="n">
-        <v>91346</v>
+        <v>91339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>126675585</v>
       </c>
       <c r="B24" t="n">
-        <v>91346</v>
+        <v>91339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>126686757</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 30224-2025 artfynd.xlsx
+++ b/artfynd/A 30224-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126686336</v>
       </c>
       <c r="B2" t="n">
-        <v>91326</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126686418</v>
+        <v>126675585</v>
       </c>
       <c r="B3" t="n">
-        <v>79632</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,40 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långsåsen, Dlr</t>
+          <t>Långsåsen, Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477668</v>
+        <v>477780</v>
       </c>
       <c r="R3" t="n">
-        <v>6731773</v>
+        <v>6731729</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -844,12 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,29 +865,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126686514</v>
+        <v>126686291</v>
       </c>
       <c r="B4" t="n">
-        <v>91346</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477553</v>
+        <v>477757</v>
       </c>
       <c r="R4" t="n">
-        <v>6731788</v>
+        <v>6731689</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,10 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126686314</v>
+        <v>126686407</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,24 +999,28 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1020,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477742</v>
+        <v>477671</v>
       </c>
       <c r="R5" t="n">
-        <v>6731707</v>
+        <v>6731781</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126686841</v>
+        <v>126686514</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,24 +1104,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1121,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477792</v>
+        <v>477553</v>
       </c>
       <c r="R6" t="n">
-        <v>6731817</v>
+        <v>6731788</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1151,12 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126686530</v>
+        <v>126686752</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,24 +1209,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1222,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477553</v>
+        <v>477575</v>
       </c>
       <c r="R7" t="n">
-        <v>6731763</v>
+        <v>6731612</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1252,12 +1270,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,48 +1303,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126675620</v>
+        <v>126686314</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långsåsen, Långsåsen, Dlr</t>
+          <t>Långsåsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477793</v>
+        <v>477742</v>
       </c>
       <c r="R8" t="n">
-        <v>6731721</v>
+        <v>6731707</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,22 +1371,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,32 +1385,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126686823</v>
+        <v>126686530</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1430,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477765</v>
+        <v>477553</v>
       </c>
       <c r="R9" t="n">
-        <v>6731828</v>
+        <v>6731763</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1460,12 +1472,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,14 +1505,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126686797</v>
+        <v>126686680</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1531,10 +1543,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477732</v>
+        <v>477539</v>
       </c>
       <c r="R10" t="n">
-        <v>6731840</v>
+        <v>6731648</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1594,32 +1606,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126686471</v>
+        <v>126686757</v>
       </c>
       <c r="B11" t="n">
-        <v>79603</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477655</v>
+        <v>477594</v>
       </c>
       <c r="R11" t="n">
-        <v>6731785</v>
+        <v>6731626</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1662,12 +1674,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1695,14 +1707,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126686832</v>
+        <v>126686767</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1733,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477784</v>
+        <v>477671</v>
       </c>
       <c r="R12" t="n">
-        <v>6731836</v>
+        <v>6731817</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1796,14 +1808,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126686767</v>
+        <v>126686777</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1834,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477671</v>
+        <v>477692</v>
       </c>
       <c r="R13" t="n">
-        <v>6731817</v>
+        <v>6731846</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1897,32 +1909,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126686450</v>
+        <v>126686786</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1947,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477654</v>
+        <v>477713</v>
       </c>
       <c r="R14" t="n">
-        <v>6731777</v>
+        <v>6731860</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1965,12 +1977,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,11 +2013,11 @@
         <v>126686794</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2099,14 +2111,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126686777</v>
+        <v>126686797</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2137,10 +2149,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477692</v>
+        <v>477732</v>
       </c>
       <c r="R16" t="n">
-        <v>6731846</v>
+        <v>6731840</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2203,11 +2215,11 @@
         <v>126686803</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2304,11 +2316,11 @@
         <v>126686813</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2402,14 +2414,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126686786</v>
+        <v>126686823</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2440,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477713</v>
+        <v>477765</v>
       </c>
       <c r="R19" t="n">
-        <v>6731860</v>
+        <v>6731828</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2503,39 +2515,35 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126686291</v>
+        <v>126686832</v>
       </c>
       <c r="B20" t="n">
-        <v>91346</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2545,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477757</v>
+        <v>477784</v>
       </c>
       <c r="R20" t="n">
-        <v>6731689</v>
+        <v>6731836</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2575,12 +2583,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,14 +2616,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126686680</v>
+        <v>126686841</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2646,10 +2654,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477539</v>
+        <v>477792</v>
       </c>
       <c r="R21" t="n">
-        <v>6731648</v>
+        <v>6731817</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2709,10 +2717,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126686407</v>
+        <v>126686450</v>
       </c>
       <c r="B22" t="n">
-        <v>91346</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,28 +2728,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2751,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477671</v>
+        <v>477654</v>
       </c>
       <c r="R22" t="n">
-        <v>6731781</v>
+        <v>6731777</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2814,10 +2818,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126686752</v>
+        <v>126686418</v>
       </c>
       <c r="B23" t="n">
-        <v>91346</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2825,28 +2829,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -2856,10 +2856,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477575</v>
+        <v>477668</v>
       </c>
       <c r="R23" t="n">
-        <v>6731612</v>
+        <v>6731773</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2919,32 +2919,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126675585</v>
+        <v>126674340</v>
       </c>
       <c r="B24" t="n">
-        <v>91346</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2954,13 +2954,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477780</v>
+        <v>477699</v>
       </c>
       <c r="R24" t="n">
-        <v>6731729</v>
+        <v>6731832</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2999,7 +2999,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Födospår.hål</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3026,32 +3031,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126674340</v>
+        <v>126675620</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,13 +3066,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477699</v>
+        <v>477793</v>
       </c>
       <c r="R25" t="n">
-        <v>6731832</v>
+        <v>6731721</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3096,7 +3101,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3106,12 +3111,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födospår.hål</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3138,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126686757</v>
+        <v>126686471</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79917</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3149,21 +3149,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477594</v>
+        <v>477655</v>
       </c>
       <c r="R26" t="n">
-        <v>6731626</v>
+        <v>6731785</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 30224-2025 artfynd.xlsx
+++ b/artfynd/A 30224-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126675585</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686291</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686407</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686514</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,6 +1330,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686752</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686314</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686530</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686680</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1704,6 +1754,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686757</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1805,6 +1860,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686767</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1906,6 +1966,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686777</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686786</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2108,6 +2178,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686794</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2209,6 +2284,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686797</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2310,6 +2390,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686803</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686813</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2512,6 +2602,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686823</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2613,6 +2708,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686832</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2714,6 +2814,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686841</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2815,6 +2920,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686450</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686418</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3028,6 +3143,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126674340</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3135,6 +3255,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126675620</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3236,8 +3361,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126686471</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>